--- a/Organizador_Imposto_de_Renda.xlsx
+++ b/Organizador_Imposto_de_Renda.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="TITULAR" sheetId="1" state="visible" r:id="rId3"/>
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Imposto de Renda</t>
   </si>
   <si>
-    <t xml:space="preserve">preencha os dados da sua pessoa física abaixo</t>
+    <t xml:space="preserve">Preencha os dados da sua pessoa física abaixo</t>
   </si>
   <si>
     <t xml:space="preserve">NOME</t>
@@ -136,7 +136,7 @@
     <t xml:space="preserve">VALOR ATUAL</t>
   </si>
   <si>
-    <t xml:space="preserve">ANEXO 📎</t>
+    <t xml:space="preserve">ANEXO</t>
   </si>
   <si>
     <t xml:space="preserve">2º Banco</t>
@@ -386,7 +386,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="000\.000\.000\-00"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
@@ -395,9 +395,10 @@
     <numFmt numFmtId="169" formatCode="\(00&quot;) &quot;0000\-0000"/>
     <numFmt numFmtId="170" formatCode="\(00&quot;) &quot;00000\-0000"/>
     <numFmt numFmtId="171" formatCode="&quot;R$ &quot;#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="General"/>
+    <numFmt numFmtId="172" formatCode="0.00%"/>
+    <numFmt numFmtId="173" formatCode="General"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,6 +453,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF6F5F80"/>
       <name val="Arial"/>
@@ -509,7 +511,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -517,7 +518,6 @@
       <color rgb="FF3A2A4A"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -525,9 +525,18 @@
       <color rgb="FF3A2A4A"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <i val="true"/>
       <sz val="8"/>
       <color rgb="FF8C8C8C"/>
@@ -536,6 +545,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF6F5F80"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
@@ -559,6 +575,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <u val="single"/>
       <sz val="10"/>
       <color rgb="FF0563C1"/>
@@ -567,6 +584,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
@@ -597,7 +622,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -618,8 +643,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCEE82"/>
         <bgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFDEE6EF"/>
       </patternFill>
     </fill>
     <fill>
@@ -630,18 +667,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFE7F3"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF9C1A83"/>
+        <bgColor rgb="FF800080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9C1A83"/>
-        <bgColor rgb="FF800080"/>
+        <fgColor rgb="FF55308D"/>
+        <bgColor rgb="FF5A3A5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEE6EF"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -655,6 +698,15 @@
       <top/>
       <bottom style="medium">
         <color rgb="FFD81B9C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
       </bottom>
       <diagonal/>
     </border>
@@ -708,144 +760,164 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="22" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -907,8 +979,8 @@
       <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF9C1A83"/>
-      <rgbColor rgb="FFEFE7F3"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFFFD7"/>
+      <rgbColor rgb="FFDEE6EF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0563C1"/>
@@ -922,7 +994,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFCEE82"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -940,10 +1012,10 @@
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF14101A"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF4A3A5A"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF5A3A5A"/>
-      <rgbColor rgb="FF4A3A5A"/>
+      <rgbColor rgb="FF55308D"/>
       <rgbColor rgb="FF3A2A4A"/>
     </indexedColors>
   </colors>
@@ -1132,193 +1204,193 @@
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:E80"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="8" t="str">
+      <c r="D7" s="10"/>
+      <c r="E7" s="9" t="str">
         <f aca="false">IF(D7="","somente números (11 dígitos)",IF(AND(ISNUMBER(D7),D7&gt;0,D7&lt;=99999999999,LEN(SUBSTITUTE(TEXT(D7,"00000000000"),LEFT(TEXT(D7,"00000000000"),1),""))&gt;0,MOD(MOD(SUMPRODUCT(--MID(TEXT(D7,"00000000000"),ROW($1:$9),1),11-ROW($1:$9))*10,11),10)=--MID(TEXT(D7,"00000000000"),10,1),MOD(MOD(SUMPRODUCT(--MID(TEXT(D7,"00000000000"),ROW($1:$10),1),12-ROW($1:$10))*10,11),10)=--MID(TEXT(D7,"00000000000"),11,1)),"✔ CPF válido","⚠ confira os dígitos do CPF"))</f>
         <v>somente números (11 dígitos)</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="11"/>
+      <c r="E8" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="str">
+      <c r="A9" s="12" t="str">
         <f aca="false">HYPERLINK("#'TITULAR'!A1","TITULAR")</f>
         <v>TITULAR</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="13"/>
+      <c r="E9" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="str">
+      <c r="A11" s="14" t="str">
         <f aca="false">HYPERLINK("#'INFORMES'!A1","INFORMES")</f>
         <v>INFORMES</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="14" t="str">
+      <c r="D12" s="15" t="str">
         <f aca="false">IF(D11="","",IFERROR(INDEX(LISTAS!$E$2:$E$10,MATCH(LEFT(D11,FIND(" ",D11&amp;" ")-1),LISTAS!$D$2:$D$10,0))&amp;" "&amp;MID(D11,FIND(" ",D11&amp;" ")+1,200),D11))</f>
         <v/>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="str">
+      <c r="A13" s="14" t="str">
         <f aca="false">HYPERLINK("#'NOTAS'!A1","NOTAS")</f>
         <v>NOTAS</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="8" t="s">
+      <c r="D14" s="17"/>
+      <c r="E14" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="18"/>
+      <c r="E15" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
-      <c r="C16" s="6" t="s">
+      <c r="A16" s="19"/>
+      <c r="C16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D21" s="20" t="str">
-        <f aca="false">HYPERLINK("#'INFORMES'!A1","PRÓXIMO →")</f>
-        <v>PRÓXIMO →</v>
+      <c r="D21" s="21" t="str">
+        <f aca="false">HYPERLINK("#'INFORMES'!A1","PRÓXIMO")</f>
+        <v>PRÓXIMO</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1385,14 +1457,6 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
   </mergeCells>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(E7,1)="⚠"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEFT(E7,1)="✔"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation allowBlank="false" error="Informe o nome completo (nome e sobrenome)." errorStyle="stop" errorTitle="Nome inválido" operator="between" prompt="Nome completo do titular." promptTitle="Nome" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D6" type="custom">
       <formula1>AND(LEN(TRIM(D6))&gt;=5,ISNUMBER(FIND(" ",TRIM(D6))))</formula1>
@@ -1455,358 +1519,365 @@
     <tabColor rgb="FFD81B9C"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="22" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="22" t="n">
-        <f aca="false">SUMIF($C$10:$C$59,"VALOR ATUAL",$D$10:$D$59)</f>
+      <c r="D6" s="23" t="n">
+        <f aca="false">SUMIF($C$9:$C$57,"VALOR ATUAL",$D$9:$D$57)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="8" t="str">
-        <f aca="false">SUMPRODUCT(($C$10:$C$59="BANCO")*($D$10:$D$59&lt;&gt;""))&amp;" banco(s) informado(s)"</f>
+      <c r="E6" s="24" t="str">
+        <f aca="false">SUMPRODUCT(($C$9:$C$57="BANCO")*($D$9:$D$57&lt;&gt;""))&amp;" banco(s) informado(s)"</f>
         <v>0 banco(s) informado(s)</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="str">
+    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="str">
         <f aca="false">HYPERLINK("#'TITULAR'!A1","TITULAR")</f>
         <v>TITULAR</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C8" s="25" t="s">
         <v>34</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="27" t="str">
+        <f aca="false">IF(AND(D9="",D10="",D11=""),"",IF(D9="","⚠ escolha o banco",IF(OR(D10="",D11=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+        <v/>
+      </c>
+    </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="24" t="str">
-        <f aca="false">IF(AND(D10="",D11="",D12=""),"",IF(D10="","⚠ escolha o banco",IF(OR(D11="",D12=""),"⚠ falta valor ou anexo","✔ completo")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="str">
+      <c r="A10" s="12" t="str">
         <f aca="false">HYPERLINK("#'INFORMES'!A1","INFORMES")</f>
         <v>INFORMES</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="25"/>
+      <c r="D10" s="28"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="str">
+      <c r="A12" s="14" t="str">
         <f aca="false">HYPERLINK("#'NOTAS'!A1","NOTAS")</f>
         <v>NOTAS</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C13" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C14" s="23" t="s">
-        <v>38</v>
+      <c r="C14" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="27" t="str">
+        <f aca="false">IF(AND(D14="",D15="",D16=""),"",IF(D14="","⚠ escolha o banco",IF(OR(D15="",D16=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="19"/>
+      <c r="C15" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="28"/>
+    </row>
+    <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="24" t="str">
-        <f aca="false">IF(AND(D15="",D16="",D17=""),"",IF(D15="","⚠ escolha o banco",IF(OR(D16="",D17=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D19" s="8"/>
+      <c r="E19" s="27" t="str">
+        <f aca="false">IF(AND(D19="",D20="",D21=""),"",IF(D19="","⚠ escolha o banco",IF(OR(D20="",D21=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
-      <c r="C16" s="6" t="s">
+    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C20" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="25"/>
-    </row>
-    <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="D20" s="28"/>
+    </row>
+    <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C21" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C20" s="6" t="s">
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C23" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C24" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="24" t="str">
-        <f aca="false">IF(AND(D20="",D21="",D22=""),"",IF(D20="","⚠ escolha o banco",IF(OR(D21="",D22=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D24" s="8"/>
+      <c r="E24" s="27" t="str">
+        <f aca="false">IF(AND(D24="",D25="",D26=""),"",IF(D24="","⚠ escolha o banco",IF(OR(D25="",D26=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C21" s="6" t="s">
+    <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C25" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="25"/>
-    </row>
-    <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C22" s="6" t="s">
+      <c r="D25" s="28"/>
+    </row>
+    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C26" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C24" s="23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C25" s="6" t="s">
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C28" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C29" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="24" t="str">
-        <f aca="false">IF(AND(D25="",D26="",D27=""),"",IF(D25="","⚠ escolha o banco",IF(OR(D26="",D27=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D29" s="8"/>
+      <c r="E29" s="27" t="str">
+        <f aca="false">IF(AND(D29="",D30="",D31=""),"",IF(D29="","⚠ escolha o banco",IF(OR(D30="",D31=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C26" s="6" t="s">
+    <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C30" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="25"/>
-    </row>
-    <row r="27" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C27" s="6" t="s">
+      <c r="D30" s="28"/>
+    </row>
+    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C31" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C30" s="6" t="s">
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C33" s="25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="24" t="str">
-        <f aca="false">IF(AND(D30="",D31="",D32=""),"",IF(D30="","⚠ escolha o banco",IF(OR(D31="",D32=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D34" s="8"/>
+      <c r="E34" s="27" t="str">
+        <f aca="false">IF(AND(D34="",D35="",D36=""),"",IF(D34="","⚠ escolha o banco",IF(OR(D35="",D36=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C31" s="6" t="s">
+    <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="25"/>
-    </row>
-    <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C32" s="6" t="s">
+      <c r="D35" s="28"/>
+    </row>
+    <row r="36" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="7"/>
-    </row>
-    <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C34" s="23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C35" s="6" t="s">
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C38" s="25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C39" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="24" t="str">
-        <f aca="false">IF(AND(D35="",D36="",D37=""),"",IF(D35="","⚠ escolha o banco",IF(OR(D36="",D37=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D39" s="8"/>
+      <c r="E39" s="27" t="str">
+        <f aca="false">IF(AND(D39="",D40="",D41=""),"",IF(D39="","⚠ escolha o banco",IF(OR(D40="",D41=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C36" s="6" t="s">
+    <row r="40" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C40" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="25"/>
-    </row>
-    <row r="37" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C37" s="6" t="s">
+      <c r="D40" s="28"/>
+    </row>
+    <row r="41" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C41" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="7"/>
-    </row>
-    <row r="38" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C39" s="23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C40" s="6" t="s">
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C43" s="25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C44" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="24" t="str">
-        <f aca="false">IF(AND(D40="",D41="",D42=""),"",IF(D40="","⚠ escolha o banco",IF(OR(D41="",D42=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D44" s="8"/>
+      <c r="E44" s="27" t="str">
+        <f aca="false">IF(AND(D44="",D45="",D46=""),"",IF(D44="","⚠ escolha o banco",IF(OR(D45="",D46=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C41" s="6" t="s">
+    <row r="45" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C45" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D41" s="25"/>
-    </row>
-    <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C42" s="6" t="s">
+      <c r="D45" s="28"/>
+    </row>
+    <row r="46" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C46" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="43" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C44" s="23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C45" s="6" t="s">
+      <c r="D46" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C48" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C49" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D45" s="7"/>
-      <c r="E45" s="24" t="str">
-        <f aca="false">IF(AND(D45="",D46="",D47=""),"",IF(D45="","⚠ escolha o banco",IF(OR(D46="",D47=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D49" s="8"/>
+      <c r="E49" s="27" t="str">
+        <f aca="false">IF(AND(D49="",D50="",D51=""),"",IF(D49="","⚠ escolha o banco",IF(OR(D50="",D51=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C46" s="6" t="s">
+    <row r="50" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C50" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="25"/>
-    </row>
-    <row r="47" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C47" s="6" t="s">
+      <c r="D50" s="28"/>
+    </row>
+    <row r="51" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C51" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C49" s="23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C50" s="6" t="s">
+      <c r="D51" s="8"/>
+    </row>
+    <row r="52" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C53" s="25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C54" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D50" s="7"/>
-      <c r="E50" s="24" t="str">
-        <f aca="false">IF(AND(D50="",D51="",D52=""),"",IF(D50="","⚠ escolha o banco",IF(OR(D51="",D52=""),"⚠ falta valor ou anexo","✔ completo")))</f>
+      <c r="D54" s="8"/>
+      <c r="E54" s="27" t="str">
+        <f aca="false">IF(AND(D54="",D55="",D56=""),"",IF(D54="","⚠ escolha o banco",IF(OR(D55="",D56=""),"⚠ falta valor ou anexo","✔ completo")))</f>
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C51" s="6" t="s">
+    <row r="55" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C55" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="25"/>
-    </row>
-    <row r="52" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C52" s="6" t="s">
+      <c r="D55" s="28"/>
+    </row>
+    <row r="56" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C56" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D52" s="7"/>
-    </row>
-    <row r="53" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C54" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C55" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D55" s="7"/>
-      <c r="E55" s="24" t="str">
-        <f aca="false">IF(AND(D55="",D56="",D57=""),"",IF(D55="","⚠ escolha o banco",IF(OR(D56="",D57=""),"⚠ falta valor ou anexo","✔ completo")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C56" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D56" s="25"/>
-    </row>
-    <row r="57" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C58" s="29" t="str">
+        <f aca="false">HYPERLINK("#'TITULAR'!A1","ANTERIOR")</f>
+        <v>ANTERIOR</v>
+      </c>
+      <c r="E58" s="21" t="str">
+        <f aca="false">HYPERLINK("#'NOTAS'!A1","PRÓXIMO")</f>
+        <v>PRÓXIMO</v>
+      </c>
+    </row>
     <row r="59" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="60" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="61" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1827,104 +1898,103 @@
     <row r="76" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="77" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="78" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C7:D7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E10:E59">
+  <conditionalFormatting sqref="E9:E57">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(E10,1)="⚠"</formula>
+      <formula>LEFT(E9,1)="⚠"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEFT(E10,1)="✔"</formula>
+      <formula>LEFT(E9,1)="✔"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="21">
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D9" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Informe um valor numérico maior ou igual a zero." errorStyle="stop" errorTitle="Valor inválido" operator="greaterThanOrEqual" prompt="Saldo em 31/12 do ano-calendário." promptTitle="Valor" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D11 D16 D21 D26 D31 D36 D41 D46 D51 D56" type="decimal">
+    <dataValidation allowBlank="false" error="Informe um valor numérico maior ou igual a zero." errorStyle="stop" errorTitle="Valor inválido" operator="greaterThanOrEqual" prompt="Saldo em 31/12 do ano-calendário." promptTitle="Valor" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D10 D15 D20 D25 D30 D35 D40 D45 D50 D55" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D12" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D11" type="custom">
       <formula1>OR(RIGHT(LOWER(D12),4)=".pdf",RIGHT(LOWER(D12),4)=".png",RIGHT(LOWER(D12),4)=".jpg",RIGHT(LOWER(D12),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D15" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D14" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D17" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D16" type="custom">
       <formula1>OR(RIGHT(LOWER(D17),4)=".pdf",RIGHT(LOWER(D17),4)=".png",RIGHT(LOWER(D17),4)=".jpg",RIGHT(LOWER(D17),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D20" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D19" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D22" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D21" type="custom">
       <formula1>OR(RIGHT(LOWER(D22),4)=".pdf",RIGHT(LOWER(D22),4)=".png",RIGHT(LOWER(D22),4)=".jpg",RIGHT(LOWER(D22),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D25" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D24" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D27" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D26" type="custom">
       <formula1>OR(RIGHT(LOWER(D27),4)=".pdf",RIGHT(LOWER(D27),4)=".png",RIGHT(LOWER(D27),4)=".jpg",RIGHT(LOWER(D27),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D30" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D29" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D32" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D31" type="custom">
       <formula1>OR(RIGHT(LOWER(D32),4)=".pdf",RIGHT(LOWER(D32),4)=".png",RIGHT(LOWER(D32),4)=".jpg",RIGHT(LOWER(D32),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D35" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D34" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D37" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D36" type="custom">
       <formula1>OR(RIGHT(LOWER(D37),4)=".pdf",RIGHT(LOWER(D37),4)=".png",RIGHT(LOWER(D37),4)=".jpg",RIGHT(LOWER(D37),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D40" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D39" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D42" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D41" type="custom">
       <formula1>OR(RIGHT(LOWER(D42),4)=".pdf",RIGHT(LOWER(D42),4)=".png",RIGHT(LOWER(D42),4)=".jpg",RIGHT(LOWER(D42),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D45" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D44" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D47" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D46" type="custom">
       <formula1>OR(RIGHT(LOWER(D47),4)=".pdf",RIGHT(LOWER(D47),4)=".png",RIGHT(LOWER(D47),4)=".jpg",RIGHT(LOWER(D47),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D50" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D49" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D52" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D51" type="custom">
       <formula1>OR(RIGHT(LOWER(D52),4)=".pdf",RIGHT(LOWER(D52),4)=".png",RIGHT(LOWER(D52),4)=".jpg",RIGHT(LOWER(D52),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D55" type="list">
+    <dataValidation allowBlank="false" error="Escolha um banco da lista." errorStyle="stop" errorTitle="Banco inválido" operator="between" prompt="Selecione o banco na lista." promptTitle="Banco" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D54" type="list">
       <formula1>LISTAS!$B$2:$B$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D57" type="custom">
+    <dataValidation allowBlank="false" error="Digite o nome do arquivo com extensão .pdf, .png, .jpg ou .jpeg." errorStyle="stop" errorTitle="Anexo inválido" operator="between" prompt="Nome do arquivo do informe. Ex.: informe_banco_2025.pdf" promptTitle="Anexo" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D56" type="custom">
       <formula1>OR(RIGHT(LOWER(D57),4)=".pdf",RIGHT(LOWER(D57),4)=".png",RIGHT(LOWER(D57),4)=".jpg",RIGHT(LOWER(D57),5)=".jpeg")</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1945,267 +2015,271 @@
     <tabColor rgb="FFD81B9C"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F1048576"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <f aca="false">COUNTIF($E$21:$E$40,"Pendente")+COUNTIF($E$21:$E$40,"Em andamento")</f>
+      <c r="D6" s="31" t="n">
+        <f aca="false">COUNTIF($E$18:$E$37,"Pendente")+COUNTIF($E$18:$E$37,"Em andamento")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <f aca="false">COUNTIF($E$21:$E$40,"Concluído")</f>
+      <c r="D7" s="31" t="n">
+        <f aca="false">COUNTIF($E$18:$E$37,"Concluído")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="str">
+      <c r="A9" s="14" t="str">
         <f aca="false">HYPERLINK("#'TITULAR'!A1","TITULAR")</f>
         <v>TITULAR</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="32" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="str">
+      <c r="A11" s="14" t="str">
         <f aca="false">HYPERLINK("#'INFORMES'!A1","INFORMES")</f>
         <v>INFORMES</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="str">
+      <c r="A13" s="12" t="str">
         <f aca="false">HYPERLINK("#'NOTAS'!A1","NOTAS")</f>
         <v>NOTAS</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C14" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="34"/>
+    </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="23" t="s">
-        <v>60</v>
+      <c r="A15" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
+      <c r="A16" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C20" s="30" t="s">
+      <c r="C17" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D17" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E17" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F17" s="35" t="s">
         <v>65</v>
       </c>
     </row>
+    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C18" s="8"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="8"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C20" s="8"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="11"/>
+    </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C21" s="7"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C22" s="7"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C23" s="7"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C24" s="7"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C25" s="7"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="10"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C26" s="7"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="10"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C27" s="7"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="10"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C28" s="7"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="10"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="7"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="10"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C30" s="7"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="10"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C31" s="7"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="10"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C32" s="7"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="10"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C33" s="7"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="10"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C34" s="7"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="10"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C35" s="7"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C36" s="7"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="10"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C37" s="7"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="10"/>
-    </row>
-    <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C38" s="7"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="10"/>
-    </row>
-    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C39" s="7"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C40" s="7"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="10"/>
-    </row>
+      <c r="C37" s="8"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C39" s="29" t="str">
+        <f aca="false">HYPERLINK("#'INFORMES'!A1","ANTERIOR")</f>
+        <v>ANTERIOR</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2243,41 +2317,42 @@
     <row r="75" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="76" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="77" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C14:D14"/>
   </mergeCells>
-  <conditionalFormatting sqref="E21:E40">
+  <conditionalFormatting sqref="E18:E37">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>E21="Concluído"</formula>
+      <formula>E18="Concluído"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>E21="Pendente"</formula>
+      <formula>E18="Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F40">
+  <conditionalFormatting sqref="F18:F37">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND(F21&lt;&gt;"",F21&lt;TODAY(),E21&lt;&gt;"Concluído")</formula>
+      <formula>AND(F18&lt;&gt;"",F18&lt;TODAY(),E18&lt;&gt;"Concluído")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="false" error="Use no máximo 60 caracteres." errorStyle="stop" errorTitle="Texto longo" operator="lessThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C21:C40" type="textLength">
+    <dataValidation allowBlank="false" error="Use no máximo 60 caracteres." errorStyle="stop" errorTitle="Texto longo" operator="lessThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C18:C37" type="textLength">
       <formula1>60</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Use no máximo 250 caracteres." errorStyle="stop" errorTitle="Texto longo" operator="lessThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D21:D40" type="textLength">
+    <dataValidation allowBlank="false" error="Use no máximo 250 caracteres." errorStyle="stop" errorTitle="Texto longo" operator="lessThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D18:D37" type="textLength">
       <formula1>250</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Escolha um status da lista." errorStyle="stop" errorTitle="Status inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E21:E40" type="list">
+    <dataValidation allowBlank="false" error="Escolha um status da lista." errorStyle="stop" errorTitle="Status inválido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E18:E37" type="list">
       <formula1>LISTAS!$C$2:$C$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Informe uma data válida (dd/mm/aaaa)." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F21:F40" type="date">
+    <dataValidation allowBlank="false" error="Informe uma data válida (dd/mm/aaaa)." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F18:F37" type="date">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2305,327 +2380,327 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="2" width="32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="38" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="39" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="39" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34" t="s">
+      <c r="A4" s="39"/>
+      <c r="B4" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="39" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34" t="s">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34" t="s">
+      <c r="C5" s="39"/>
+      <c r="D5" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="39" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34" t="s">
+      <c r="A6" s="39"/>
+      <c r="B6" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34" t="s">
+      <c r="C6" s="39"/>
+      <c r="D6" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="39" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34" t="s">
+      <c r="A7" s="39"/>
+      <c r="B7" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34" t="s">
+      <c r="C7" s="39"/>
+      <c r="D7" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="39" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34" t="s">
+      <c r="A8" s="39"/>
+      <c r="B8" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34" t="s">
+      <c r="C8" s="39"/>
+      <c r="D8" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="39" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34" t="s">
+      <c r="A9" s="39"/>
+      <c r="B9" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34" t="s">
+      <c r="C9" s="39"/>
+      <c r="D9" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="39" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="39" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34" t="s">
+      <c r="A11" s="39"/>
+      <c r="B11" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34" t="s">
+      <c r="A12" s="39"/>
+      <c r="B12" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34" t="s">
+      <c r="A13" s="39"/>
+      <c r="B13" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34" t="s">
+      <c r="A14" s="39"/>
+      <c r="B14" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34" t="s">
+      <c r="A15" s="39"/>
+      <c r="B15" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34" t="s">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34" t="s">
+      <c r="A17" s="39"/>
+      <c r="B17" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34" t="s">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34" t="s">
+      <c r="A19" s="39"/>
+      <c r="B19" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34" t="s">
+      <c r="A20" s="39"/>
+      <c r="B20" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34" t="s">
+      <c r="A21" s="39"/>
+      <c r="B21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34" t="s">
+      <c r="A22" s="39"/>
+      <c r="B22" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34" t="s">
+      <c r="A23" s="39"/>
+      <c r="B23" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34" t="s">
+      <c r="A24" s="39"/>
+      <c r="B24" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34"/>
-      <c r="B25" s="34" t="s">
+      <c r="A25" s="39"/>
+      <c r="B25" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
